--- a/src/ii_skills/shared/excel_templates/09_horizontal_bar_pie.xlsx
+++ b/src/ii_skills/shared/excel_templates/09_horizontal_bar_pie.xlsx
@@ -29,13 +29,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +46,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,14 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -143,195 +152,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Market Ranking</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Rankings'!B2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Rankings'!$A$3:$A$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Rankings'!$B$3:$B$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Exposure Breakdown</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Rankings'!G2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Rankings'!$F$3:$F$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Rankings'!$G$3:$G$4</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,219 +443,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BAR CHART DATA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PIE CHART DATA</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Market Ranking Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Annotation</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Is_Subject</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>City A</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="C3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Market A</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>#1 in Region</t>
         </is>
       </c>
-      <c r="D3" t="b">
+      <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Top Markets</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>City B</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="b">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Market B</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Other Markets</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>City C</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="b">
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Market C</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>City D</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Market D</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>#1 in Province</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>City E</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>City F</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>City G</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>City H</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>#4 in Ontario</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>City I</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="b">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Market E</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>